--- a/Python Module.xlsx
+++ b/Python Module.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Harikrishnan\Document\Learning\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2288C445-6FEB-4E00-9743-5A0056DD0023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0674074A-5D21-4DA8-88DB-8119D16FB1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CED3EA6-3FAB-45BB-ADA0-15199DCB0CB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CED3EA6-3FAB-45BB-ADA0-15199DCB0CB5}"/>
   </bookViews>
   <sheets>
-    <sheet name="math" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="random" sheetId="4" r:id="rId1"/>
+    <sheet name="math" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="165">
   <si>
     <t>Functions</t>
   </si>
@@ -850,6 +851,254 @@
   </si>
   <si>
     <t>Constant</t>
+  </si>
+  <si>
+    <t>random()</t>
+  </si>
+  <si>
+    <t>Returns a random float between 0.0 and 1.0.</t>
+  </si>
+  <si>
+    <t>import random
+print(random.random())  # e.g., 0.3745</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>randint(a, b)</t>
+  </si>
+  <si>
+    <t>import random
+print(random.randint(1, 10))  # e.g., 7</t>
+  </si>
+  <si>
+    <t>randrange(start, stop, step)</t>
+  </si>
+  <si>
+    <t>randrange()</t>
+  </si>
+  <si>
+    <t>randint()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns a random integer between </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (inclusive).</t>
+    </r>
+  </si>
+  <si>
+    <t>Returns a random number from a range with a step.</t>
+  </si>
+  <si>
+    <t>import random
+print(random.randrange(0, 10, 2))  # e.g., 4 (even numbers 0-8)</t>
+  </si>
+  <si>
+    <t>choice(seq)</t>
+  </si>
+  <si>
+    <t>choice()</t>
+  </si>
+  <si>
+    <t>Returns a random element from a sequence (list, tuple, string).</t>
+  </si>
+  <si>
+    <t>import random
+items = ['apple', 'banana', 'cherry']
+print(random.choice(items))  # e.g., 'banana'</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>choices(population, weights=None, k=1)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns a list of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> elements with replacement, optionally weighted.</t>
+    </r>
+  </si>
+  <si>
+    <t>import random
+items = ['apple', 'banana', 'cherry']
+print(random.choices(items, k=2))  # e.g., ['cherry', 'banana']</t>
+  </si>
+  <si>
+    <t>['apple', 'apple']</t>
+  </si>
+  <si>
+    <t>sample(population, k)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns a list of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unique elements (without replacement).</t>
+    </r>
+  </si>
+  <si>
+    <t>import random
+items = ['apple', 'banana', 'cherry']
+print(random.sample(items, 2))  # e.g., ['banana', 'apple']</t>
+  </si>
+  <si>
+    <t>['apple', 'cherry']</t>
+  </si>
+  <si>
+    <t>sample()</t>
+  </si>
+  <si>
+    <t>shuffle(x)</t>
+  </si>
+  <si>
+    <t>Shuffles a list in place.</t>
+  </si>
+  <si>
+    <t>import random
+cards = [1, 2, 3, 4, 5]
+random.shuffle(cards)
+print(cards)  # e.g., [3, 1, 5, 2, 4]</t>
+  </si>
+  <si>
+    <t>[1, 5, 2, 4, 3]</t>
+  </si>
+  <si>
+    <t>uniform(a, b)</t>
+  </si>
+  <si>
+    <t>uniform()</t>
+  </si>
+  <si>
+    <t>shuffle()</t>
+  </si>
+  <si>
+    <t>import random
+print(random.uniform(1.5, 5.5))  # e.g., 3.728</t>
+  </si>
+  <si>
+    <t>seed(a=None)</t>
+  </si>
+  <si>
+    <t>seed()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns a random float between </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sets the seed for reproducibility.</t>
+  </si>
+  <si>
+    <t>import random
+random.seed(10)
+print(random.random())  # always same output for the same seed</t>
   </si>
 </sst>
 </file>
@@ -929,7 +1178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -955,6 +1204,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1289,6 +1541,209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C934045-05FF-4210-8158-62207BC62C8B}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A2" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6" ht="31.2">
+      <c r="A3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.50837357343842404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.2">
+      <c r="A4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="46.8">
+      <c r="A5" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="46.8">
+      <c r="A6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="62.4">
+      <c r="A7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="62.4">
+      <c r="A8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="62.4">
+      <c r="A9" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="31.2">
+      <c r="A10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4.0313168694340904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="62.4">
+      <c r="A11" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.57140259468991295</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEC7921-BA36-4A45-8BC0-808C0D35D2A9}">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -1787,7 +2242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FFEDB6-E341-4091-95D4-D478ABE8D506}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.6"/>

--- a/Python Module.xlsx
+++ b/Python Module.xlsx
@@ -8,14 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Harikrishnan\Document\Learning\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0674074A-5D21-4DA8-88DB-8119D16FB1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772EE0A9-C371-4570-AE07-578135CBB504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CED3EA6-3FAB-45BB-ADA0-15199DCB0CB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CED3EA6-3FAB-45BB-ADA0-15199DCB0CB5}"/>
   </bookViews>
   <sheets>
-    <sheet name="random" sheetId="4" r:id="rId1"/>
-    <sheet name="math" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="collections" sheetId="15" r:id="rId1"/>
+    <sheet name="python-docx" sheetId="8" r:id="rId2"/>
+    <sheet name="PyPDF2" sheetId="9" r:id="rId3"/>
+    <sheet name="json" sheetId="10" r:id="rId4"/>
+    <sheet name="dotenv" sheetId="14" r:id="rId5"/>
+    <sheet name="logging" sheetId="11" r:id="rId6"/>
+    <sheet name="sys" sheetId="7" r:id="rId7"/>
+    <sheet name="os" sheetId="6" r:id="rId8"/>
+    <sheet name="date &amp; time" sheetId="5" r:id="rId9"/>
+    <sheet name="random" sheetId="4" r:id="rId10"/>
+    <sheet name="math" sheetId="1" r:id="rId11"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,8 +46,100 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="8">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="8">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="405">
   <si>
     <t>Functions</t>
   </si>
@@ -1100,12 +1201,1262 @@
 random.seed(10)
 print(random.random())  # always same output for the same seed</t>
   </si>
+  <si>
+    <t>choices()</t>
+  </si>
+  <si>
+    <t>Date and Time</t>
+  </si>
+  <si>
+    <t>datetime.now()</t>
+  </si>
+  <si>
+    <t>Returns the current local date and time.</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.now())   # 2025-09-28 08:25:30.123456</t>
+  </si>
+  <si>
+    <t>datetime.today()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Returns the current local date and time (similar to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>now()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, but without timezone support).</t>
+    </r>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.today())   # 2025-09-28 08:25:30.123456</t>
+  </si>
+  <si>
+    <t># 2025-09-28 08:25:30.123456</t>
+  </si>
+  <si>
+    <t>datetime.date()</t>
+  </si>
+  <si>
+    <t>Extracts the date part (year, month, day).</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.now().date())   # 2025-09-28</t>
+  </si>
+  <si>
+    <t># 2025-09-28</t>
+  </si>
+  <si>
+    <t>datetime.time()</t>
+  </si>
+  <si>
+    <t>Extracts the time part (hour, minute, second, microsecond).</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.now().time())   # 08:25:30.123456</t>
+  </si>
+  <si>
+    <t># 08:26:56.583781</t>
+  </si>
+  <si>
+    <t>datetime.strptime()</t>
+  </si>
+  <si>
+    <t>Converts a string into a datetime object using a format.</t>
+  </si>
+  <si>
+    <t>from datetime import datetime
+dt = datetime.strptime("28-09-2025", "%d-%m-%Y")
+print(dt)   # 2025-09-28 00:00:00</t>
+  </si>
+  <si>
+    <t># 2025-09-28 00:00:00</t>
+  </si>
+  <si>
+    <t>datetime.strftime()</t>
+  </si>
+  <si>
+    <t>Converts a datetime object to a formatted string.</t>
+  </si>
+  <si>
+    <t># 28/09/2025 08:34:04</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.now().strftime("%d/%m/%Y %H:%M:%S")) # 28/09/2025 08:25:30</t>
+  </si>
+  <si>
+    <t>datetime.timedelta</t>
+  </si>
+  <si>
+    <t>Represents the difference between two dates/times.</t>
+  </si>
+  <si>
+    <t>from datetime import *
+today = datetime.now()
+future = today + timedelta(days=5)
+print(future)   # 2025-10-03 …</t>
+  </si>
+  <si>
+    <t># 2025-10-03 08:36:13.036834</t>
+  </si>
+  <si>
+    <t>datetime.replace()</t>
+  </si>
+  <si>
+    <t>Replaces specific parts of a datetime (like year, month, day).</t>
+  </si>
+  <si>
+    <t>from datetime import *
+dt = datetime.now()
+print(dt.replace(year=2030))   # Replace year with 2030</t>
+  </si>
+  <si>
+    <t># 2030-09-28 08:38:11.421943</t>
+  </si>
+  <si>
+    <t>weekday() → Monday = 0, Sunday = 6
+isoweekday() → Monday = 1, Sunday = 7</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">datetime.weekday() / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>isoweekday()</t>
+    </r>
+  </si>
+  <si>
+    <t>6
+7</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.now().weekday())    # e.g., 6 (Sunday)
+print(datetime.now().isoweekday()) # e.g., 7 (Sunday)</t>
+  </si>
+  <si>
+    <r>
+      <t>datetime.utcfromtimestamp()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fromtimestamp()</t>
+    </r>
+  </si>
+  <si>
+    <t>Converts a timestamp into a datetime.</t>
+  </si>
+  <si>
+    <t>from datetime import *
+print(datetime.fromtimestamp(1632806400))  # Local time
+print(datetime.utcfromtimestamp(1632806400))  # UTC time</t>
+  </si>
+  <si>
+    <t># 2021-09-28 10:50:00
+# 2021-09-28 05:20:00</t>
+  </si>
+  <si>
+    <t>File and Directory Operations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>OS:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The os module in Python is a built-in library that allows interaction with the operating system. It provides functions for handling files, directories, and environment variables. This makes Python programs portable across Windows, macOS, and Linux without OS-specific code. </t>
+    </r>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/68d8acc5-f744-8006-a617-754feb61e85e</t>
+  </si>
+  <si>
+    <t>os.getcwd()</t>
+  </si>
+  <si>
+    <t>Returns the current working directory.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.getcwd())  # Example: C:\Users\Hari</t>
+  </si>
+  <si>
+    <t>C:\Harikrishnan\pythonProject\pythonProject6</t>
+  </si>
+  <si>
+    <t>os.chdir(path)</t>
+  </si>
+  <si>
+    <t>Changes the current working directory.</t>
+  </si>
+  <si>
+    <t>import os
+os.chdir("C:/Users/Hari/Desktop")</t>
+  </si>
+  <si>
+    <t>os.listdir(path=".")</t>
+  </si>
+  <si>
+    <t>Lists all files and directories in the given path.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.listdir("."))  # List current directory</t>
+  </si>
+  <si>
+    <t>['.env', '.idea', 'app.log', 'calculate.py', 'client.py', 'main.py', 'ratio_proportion.tex', '__pycache__']</t>
+  </si>
+  <si>
+    <t>import os
+print(os.listdir("C:\Harikrishnan\Document\Learning\Python"))  # List current directory</t>
+  </si>
+  <si>
+    <t>['Fundamental of python.docx', 'Inbuiltfunction.docx', 'Numpy Module.docx', 'Python 2.docx', 'Python Module.xlsx', 'Python_Modules_Complete_Roadmap.pdf', 'Statistics Module.docx', 'String Module.docx', 'Turtle Module.docx', '~$Python Module.xlsx']</t>
+  </si>
+  <si>
+    <t>os.mkdir(path)</t>
+  </si>
+  <si>
+    <t>Creates a new directory.</t>
+  </si>
+  <si>
+    <t>os.chdir()</t>
+  </si>
+  <si>
+    <t>os.listdir()</t>
+  </si>
+  <si>
+    <t>os.mkdir()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">import os
+os.mkdir(r"C:\Harikrishnan\Document\Learning\Python\new_folder")
+</t>
+  </si>
+  <si>
+    <t>os.makedirs(path)</t>
+  </si>
+  <si>
+    <t>os.makedirs()</t>
+  </si>
+  <si>
+    <t>Creates directories recursively.</t>
+  </si>
+  <si>
+    <t>import os
+os.makedirs("folder1/folder2")</t>
+  </si>
+  <si>
+    <t>os.rmdir(path)</t>
+  </si>
+  <si>
+    <t>Removes a directory (only if empty).</t>
+  </si>
+  <si>
+    <t>os.rmdir()</t>
+  </si>
+  <si>
+    <t>import os
+os.rmdir(r"C:\Harikrishnan\Document\Learning\Python\new_folder")</t>
+  </si>
+  <si>
+    <t>os.remove(path)</t>
+  </si>
+  <si>
+    <t>Removes a file.</t>
+  </si>
+  <si>
+    <t>os.remove()</t>
+  </si>
+  <si>
+    <t>import os
+os.remove(r"C:\Harikrishnan\Document\Learning\Python\garage text.txt")</t>
+  </si>
+  <si>
+    <t>Renames a file or directory.</t>
+  </si>
+  <si>
+    <t>os.rename(src, dst)</t>
+  </si>
+  <si>
+    <t>os.rename()</t>
+  </si>
+  <si>
+    <t>import os
+os.rename(r"C:\Harikrishnan\Document\Learning\Python\test 1.docx", r"C:\Harikrishnan\Document\Learning\Python\hari_test.docx")</t>
+  </si>
+  <si>
+    <t>os.path.exists(path)</t>
+  </si>
+  <si>
+    <t>Checks if a path exists.</t>
+  </si>
+  <si>
+    <t>os.path.exists()</t>
+  </si>
+  <si>
+    <t>import os
+print(os.path.exists(r"C:\Harikrishnan\Document\Learning\Python\hari_test.docx"))</t>
+  </si>
+  <si>
+    <t>os.path.isfile(path)</t>
+  </si>
+  <si>
+    <t>Checks if path is a file.</t>
+  </si>
+  <si>
+    <t>os.path.isfile()</t>
+  </si>
+  <si>
+    <t>os.path.isdir(path)</t>
+  </si>
+  <si>
+    <t>Checks if path is a  directory.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.path.isdir(r"C:\Harikrishnan\Document\Learning\Python"))</t>
+  </si>
+  <si>
+    <t>Environment and System</t>
+  </si>
+  <si>
+    <t>os.environ</t>
+  </si>
+  <si>
+    <t>Access environment variables.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.environ["PATH"])</t>
+  </si>
+  <si>
+    <t>C:\Program Files (x86)\Common Files\Intel\Shared Files\cpp\bin\Intel64;C:\Program Files (x86)\Microsoft SDKs\Azure\CLI2\wbin;C:\Program Files\Python39\Scripts\;C:\Program Files\Python39\;C:\windows\system32;C:\windows;C:\windows\System32\Wbem;C:\windows\System32\WindowsPowerShell\v1.0\;C:\windows\System32\OpenSSH\;C:\Program Files (x86)\NVIDIA Corporation\PhysX\Common;C:\Program Files\NVIDIA Corporation\NVIDIA NvDLISR;C:\WINDOWS\system32;C:\WINDOWS;C:\WINDOWS\System32\Wbem;C:\WINDOWS\System32\WindowsPowerShell\v1.0\;C:\WINDOWS\System32\OpenSSH\;C:\Program Files\Microsoft SQL Server\Client SDK\ODBC\170\Tools\Binn\;C:\Program Files (x86)\Microsoft SQL Server\150\Tools\Binn\;C:\Program Files\Microsoft SQL Server\150\Tools\Binn\;C:\Program Files\Microsoft SQL Server\150\DTS\Binn\;C:\Program Files\Azure Data Studio\bin;C:\Program Files (x86)\MATLAB\R2010a\runtime\win32;C:\Program Files (x86)\MATLAB\R2010a\bin;C:\Program Files\dotnet\;C:\Program Files\MiKTeX\miktex\bin\x64\;C:\Program Files\MySQL\MySQL Shell 8.0\bin\;C:\Users\HARI\AppData\Local\Microsoft\WindowsApps;;C:\Program Files\JetBrains\PyCharm Community Edition 2021.2.1\bin;;C:\Program Files\Azure Data Studio\bin;C:\Users\HARI\AppData\Local\Programs\Microsoft VS Code\bin</t>
+  </si>
+  <si>
+    <t>os.name</t>
+  </si>
+  <si>
+    <r>
+      <t>Returns the name of the operating system (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'nt'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for Windows, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'posix'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for Linux/Mac).</t>
+    </r>
+  </si>
+  <si>
+    <t>nt</t>
+  </si>
+  <si>
+    <t>import os
+print(os.name)</t>
+  </si>
+  <si>
+    <t>os.system()</t>
+  </si>
+  <si>
+    <t>Executes a system command. [cmd] command prompt</t>
+  </si>
+  <si>
+    <t>import os
+os.system("echo Hello World")</t>
+  </si>
+  <si>
+    <t>Hello World</t>
+  </si>
+  <si>
+    <t>os.getlogin()</t>
+  </si>
+  <si>
+    <t>Returns the name of the user logged in.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.getlogin())</t>
+  </si>
+  <si>
+    <t>HARI</t>
+  </si>
+  <si>
+    <t>os.cpu_count()</t>
+  </si>
+  <si>
+    <t>Returns the number of CPU cores.</t>
+  </si>
+  <si>
+    <t>import os
+print(os.cpu_count())</t>
+  </si>
+  <si>
+    <t>sys</t>
+  </si>
+  <si>
+    <t>sys.argv</t>
+  </si>
+  <si>
+    <t>Returns a list of command-line arguments passed to the script.</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.argv)
+# Example: if run as "python script.py hello"
+# Output: ['script.py', 'hello']</t>
+  </si>
+  <si>
+    <t>['C:/Harikrishnan/pythonProject/pythonProject6/main.py']</t>
+  </si>
+  <si>
+    <t>sys.exit([status])</t>
+  </si>
+  <si>
+    <t>Exits from Python.
+status=0 means success, non-zero means error.</t>
+  </si>
+  <si>
+    <t>sys.exit()</t>
+  </si>
+  <si>
+    <t>Exiting program...</t>
+  </si>
+  <si>
+    <t>import sys
+print("Exiting program...")
+sys.exit(0)</t>
+  </si>
+  <si>
+    <t>sys.version</t>
+  </si>
+  <si>
+    <t>Returns Python version info as a string.</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.version)
+# Example: '3.12.2 (tags/v3.12.2:abcd123, Feb 2025) ...'</t>
+  </si>
+  <si>
+    <t>3.9.7 (tags/v3.9.7:1016ef3, Aug 30 2021, 20:19:38) [MSC v.1929 64 bit (AMD64)]</t>
+  </si>
+  <si>
+    <t>sys.maxsize</t>
+  </si>
+  <si>
+    <t>Returns the maximum size integers can take (depends on platform).</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.maxsize)  # On 64-bit, usually 9223372036854775807</t>
+  </si>
+  <si>
+    <t># 9223372036854775807</t>
+  </si>
+  <si>
+    <t>https://github.com/azurede007/pycharmworkouts</t>
+  </si>
+  <si>
+    <t>sys.path</t>
+  </si>
+  <si>
+    <t>List of directories that Python searches for modules.</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.path)  # Useful for debugging import errors</t>
+  </si>
+  <si>
+    <t>['C:\\Harikrishnan\\pythonProject\\pythonProject6', 'C:\\Harikrishnan\\pythonProject\\pythonProject6', 'C:\\Program Files\\Python39\\python39.zip', 'C:\\Program Files\\Python39\\DLLs', 'C:\\Program Files\\Python39\\lib', 'C:\\Program Files\\Python39', 'C:\\Users\\HARI\\AppData\\Roaming\\Python\\Python39\\site-packages', 'C:\\Program Files\\Python39\\lib\\site-packages']</t>
+  </si>
+  <si>
+    <t>sys.platform</t>
+  </si>
+  <si>
+    <t>Returns the name of the platform (OS).</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.platform)  # Example: 'win32', 'linux', 'darwin' (MacOS)</t>
+  </si>
+  <si>
+    <t>win32</t>
+  </si>
+  <si>
+    <t>sys.getsizeof(object)</t>
+  </si>
+  <si>
+    <t>Returns the memory size (in bytes) of an object.</t>
+  </si>
+  <si>
+    <t>sys.getsizeof()</t>
+  </si>
+  <si>
+    <t>import sys
+print(sys.getsizeof(100))      # 28 (bytes)
+print(sys.getsizeof("Hello"))  # 54 (bytes)</t>
+  </si>
+  <si>
+    <t>28
+54</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reads input directly from the terminal (like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>input()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does).</t>
+    </r>
+  </si>
+  <si>
+    <t>import sys
+print("Enter something: ")
+data = sys.stdin.readline()   # reads one line from input
+print("You typed:", data)</t>
+  </si>
+  <si>
+    <t>Enter something: 
+hari
+You typed: hari</t>
+  </si>
+  <si>
+    <t>sys.stdin (Standard Input)</t>
+  </si>
+  <si>
+    <r>
+      <t>sys.stdout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Standard Output)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Used to display output (like </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>print()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> does).</t>
+    </r>
+  </si>
+  <si>
+    <t>import sys
+sys.stdout.write("Hello from sys.stdout!\n")
+print("Hello from print()")</t>
+  </si>
+  <si>
+    <t>Hello from sys.stdout!
+Hello from print()</t>
+  </si>
+  <si>
+    <r>
+      <t>sys.stderr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Standard Error)</t>
+    </r>
+  </si>
+  <si>
+    <t>Used to print error messages (separate from normal output).
+Helpful for logging/debugging.</t>
+  </si>
+  <si>
+    <t>import sys
+sys.stdout.write("This is normal output\n")
+sys.stderr.write("This is an error message\n")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">This is normal output
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>This is an error message</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>sys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> module in Python provides functions and variables to interact with the Python interpreter. It’s widely used for system-level operations like handling command-line arguments, controlling the runtime environment, and interacting with standard I/O.</t>
+    </r>
+  </si>
+  <si>
+    <t>python-docx</t>
+  </si>
+  <si>
+    <t>Document()</t>
+  </si>
+  <si>
+    <t>Creates a new Word document.</t>
+  </si>
+  <si>
+    <t>from docx import *
+# Create a new document
+doc = Document()
+# Save the document
+doc.save(r"C:\Harikrishnan\Document\Learning\Python\test.docx")</t>
+  </si>
+  <si>
+    <t>from docx import *
+from docx.shared import Inches
+# 1. Create a new Document
+doc = Document()
+# 2. Add a Heading
+doc.add_heading("Python-Docx Full Example", level=1)
+# 3. Add a Paragraph
+para = doc.add_paragraph("This is a normal paragraph. ")
+# 4. Add a Run (with formatting)
+run = para.add_run("This text is Bold, Italic, and Underlined.")
+run.bold = True
+run.italic = True
+run.underline = True
+# 5. Add another Heading (level 2)
+doc.add_heading("Adding a Table", level=2)
+# 6. Add a Table
+table = doc.add_table(rows=2, cols=2)
+table.style = "Table Grid"
+table.cell(0, 0).text = "Row 1, Col 1"
+table.cell(0, 1).text = "Row 1, Col 2"
+table.cell(1, 0).text = "Row 2, Col 1"
+table.cell(1, 1).text = "Row 2, Col 2"
+# 7. Add a Section (for page settings)
+section = doc.sections[0]
+section.left_margin = Inches(1)
+section.right_margin = Inches(1)
+# 8. Add another Heading
+doc.add_heading("Adding a Picture", level=2)
+# 9. Add an Image (make sure test.png exists in same folder)
+# doc.add_picture("test.png", width=Inches(1.5))
+# 10. Save the Document
+doc.save(r"C:\Harikrishnan\Document\Learning\Python\test.docx")
+print("Document created successfully!")</t>
+  </si>
+  <si>
+    <t>Document() → create new doc
+add_heading() → add headings
+add_paragraph() → add paragraph
+add_run() → formatted text inside paragraph
+add_table() → insert table
+sections → set margins/page layout
+add_picture() → insert an image
+save() → save the document</t>
+  </si>
+  <si>
+    <t>Document()
+add_heading()
+add_paragraph()
+add_run()
+add_table()
+sections
+add_picture()
+save()</t>
+  </si>
+  <si>
+    <t>The python-docx package is widely used in Python to create, read, and modify Word documents (.docx). Here’s a detailed list of the most commonly used functions and methods in python-docx</t>
+  </si>
+  <si>
+    <t>Document created successfully!</t>
+  </si>
+  <si>
+    <t>PyPDF2</t>
+  </si>
+  <si>
+    <t>PdfReader()</t>
+  </si>
+  <si>
+    <t>Opens and reads a PDF file.</t>
+  </si>
+  <si>
+    <t>from PyPDF2 import *
+reader = PdfReader(r"C:\Harikrishnan\Document\Learning\Python\Python_Modules_Complete_Roadmap.pdf")
+print(len(reader.pages))   # Number of pages</t>
+  </si>
+  <si>
+    <t>PdfWriter()</t>
+  </si>
+  <si>
+    <t>Creates or writes a new PDF.</t>
+  </si>
+  <si>
+    <t>from PyPDF2 import *
+writer = PdfWriter()</t>
+  </si>
+  <si>
+    <t>Access pages of the PDF.</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>from PyPDF2 import *
+# Load the PDF
+reader = PdfReader(r"C:\Harikrishnan\Document\Learning\Python\Python_Modules_Complete_Roadmap.pdf")
+# Get total number of pages
+num_pages = len(reader.pages)
+print("Total Pages:", num_pages)
+# Access the first page
+first_page = reader.pages[0]
+print(first_page)
+# Access the last page
+last_page = reader.pages[-1]
+print(last_page)</t>
+  </si>
+  <si>
+    <t>Total Pages: 2
+{'/Contents': IndirectObject(12, 0, 2720468925264), '/MediaBox': [0, 0, 595.2756, 841.8898], '/Parent': IndirectObject(11, 0, 2720468925264), '/Resources': {'/Font': IndirectObject(1, 0, 2720468925264), '/ProcSet': ['/PDF', '/Text', '/ImageB', '/ImageC', '/ImageI']}, '/Rotate': 0, '/Trans': {}, '/Type': '/Page'}
+{'/Contents': IndirectObject(13, 0, 2720468925264), '/MediaBox': [0, 0, 595.2756, 841.8898], '/Parent': IndirectObject(11, 0, 2720468925264), '/Resources': {'/Font': IndirectObject(1, 0, 2720468925264), '/ProcSet': ['/PDF', '/Text', '/ImageB', '/ImageC', '/ImageI']}, '/Rotate': 0, '/Trans': {}, '/Type': '/Page'}</t>
+  </si>
+  <si>
+    <t>extract_text()</t>
+  </si>
+  <si>
+    <t>Extracts text from a PDF page.</t>
+  </si>
+  <si>
+    <t>from PyPDF2 import PdfReader
+# Load the PDF file
+reader = PdfReader(r"C:\Harikrishnan\Document\Learning\Python\Python_Modules_Complete_Roadmap.pdf")
+# Get the first page
+page = reader.pages[0]
+# Extract text from the page
+text = page.extract_text()
+print(text)</t>
+  </si>
+  <si>
+    <t>■ Python Modules Learning Order (Beginner →
+ Advanced → Specialized)
+Phase 1: Beginner (Foundations)
+Start with core modules you'll use everywhere:
+- math → math functions
+- random → random numbers
+- datetime → dates &amp; times
+- os → file &amp; directory handling
+- sys → system functions
+- json → JSON data handling
+- csv → CSV file handling
+- logging → debugging &amp; logs
+■ Practice: Write a script that reads a CSV file, logs errors, and processes data.
+Phase 2: Intermediate (Data &amp; Utilities)
+Next, learn data handling &amp; functional utilities:
+- collections → advanced structures (Counter, deque, etc.)
+- itertools → permutations, combinations
+- functools → higher-order functions (reduce, lru_cache)
+- statistics → basic statistics
+- shutil → file operations (copy, move)
+- pickle → object serialization
+- re → regular expressions
+■ Practice: Text analyzer (count words, find top 10 frequent words).
+Phase 3: Databases &amp; File Handling
+For working with persistent data:
+- sqlite3 → local databases
+- mysql-connector-python / PyMySQL → MySQL
+- psycopg2 → PostgreSQL
+- SQLAlchemy → ORM (optional, but very useful)
+- xml.etree.ElementTree → XML parsing
+■ Project: Employee database system.
+Phase 4: Networking &amp; Web
+For APIs, scraping, and automation:
+- http.client / urllib → basic HTTP
+- requests → APIs (must-learn)
+- BeautifulSoup (bs4) → web scraping
+- selenium → browser automation
+- socket → low-level networking
+■ Project: Web scraper that fetches live data from an API &amp; saves to DB.
+Phase 5: Data Science &amp; Visualization
+For data analysis and visualization:
+- NumPy → numerical arrays
+- Pandas → data manipulation
+- Matplotlib → visualization
+- Seaborn → advanced charts
+Process finished with exit code 0</t>
+  </si>
+  <si>
+    <t>In Python, the most important package for working with JSON is the built-in json module. It allows you to encode (serialize) Python objects into JSON and decode (deserialize) JSON back into Python objects.</t>
+  </si>
+  <si>
+    <t>json.dumps()</t>
+  </si>
+  <si>
+    <t>Converts a Python object to a JSON string.</t>
+  </si>
+  <si>
+    <t>import json
+data = {"name": "Hari", "age": 25}
+json_str = json.dumps(data)
+print(json_str)  # Output: {"name": "Hari", "age": 25}</t>
+  </si>
+  <si>
+    <t>{"name": "Hari", "age": 25}</t>
+  </si>
+  <si>
+    <t>json.dump()</t>
+  </si>
+  <si>
+    <t>Writes a Python object as JSON into a file.</t>
+  </si>
+  <si>
+    <t>with open("data.json", "w") as f:
+    json.dump(data, f)</t>
+  </si>
+  <si>
+    <t>json.loads()</t>
+  </si>
+  <si>
+    <t>Converts a JSON string back to a Python object.</t>
+  </si>
+  <si>
+    <t>json_str = '{"name": "Hari", "age": 25}'
+data = json.loads(json_str)
+print(data["name"])  # Output: Hari</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>json.load()</t>
+  </si>
+  <si>
+    <t>Reads JSON data from a file and converts it into a Python object.</t>
+  </si>
+  <si>
+    <t>with open("data.json", "r") as f:
+    data = json.load(f)
+print(data)  # Output: {'name': 'Hari', 'age': 25}</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>logging</t>
+  </si>
+  <si>
+    <t>The most important logging package in Python is the built-in logging module, which is used to track events that happen while software runs. It’s essential for debugging, monitoring, and maintaining applications.</t>
+  </si>
+  <si>
+    <t>import logging
+# Configure logging
+logging.basicConfig(level=logging.INFO, format='%(asctime)s - %(levelname)s - %(message)s')
+logging.debug("This is a debug message")   # Won't show because level=INFO
+logging.info("Program started")            # Will show
+logging.warning("This is a warning")
+logging.error("An error occurred")
+logging.critical("Critical issue!")</t>
+  </si>
+  <si>
+    <t>2025-09-30 19:15:02,116 - INFO - Program started
+2025-09-30 19:15:02,116 - WARNING - This is a warning
+2025-09-30 19:15:02,116 - ERROR - An error occurred
+2025-09-30 19:15:02,116 - CRITICAL - Critical issue!</t>
+  </si>
+  <si>
+    <t>basicConfig()
+debug()
+info()
+warning()
+error()
+critical()</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Function/Method</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Purpose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+logging.basicConfig()	Configure logging (level, format, file, etc.)
+logging.debug()	            Log a debug message
+logging.info()	            Log an info message
+logging.warning()	Log a warning message
+logging.error()	            Log an error message
+logging.critical()	            Log a critical message</t>
+    </r>
+  </si>
+  <si>
+    <t>dotenv</t>
+  </si>
+  <si>
+    <t>In Python, dotenv is used to manage environment variables from a .env file.
+It’s commonly used to store sensitive information like database credentials, API keys, or secret tokens outside your code.</t>
+  </si>
+  <si>
+    <t>from dotenv import *</t>
+  </si>
+  <si>
+    <t>It mainly used as a read config file</t>
+  </si>
+  <si>
+    <t>In pycharm,
+Right Click on the folder path. Click on new and create file in the name of .env without extension
+Create the key-value pair</t>
+  </si>
+  <si>
+    <t>.env</t>
+  </si>
+  <si>
+    <t>MYSQL_SERVERNAME=localhost
+MYSQL_USERNAME=root
+MYSQL_PASSWORD=Root2001!
+MYSQL_DBNAME=sample</t>
+  </si>
+  <si>
+    <t>from dotenv import *
+import os
+load_dotenv()  # loads variables from .env file
+print(os.getenv("MYSQL_SERVERNAME"))  # localhost
+print(os.getenv("MYSQL_USERNAME"))    # root
+print(os.getenv("MYSQL_PASSWORD"))    # Root2001!
+print(os.getenv("MYSQL_DBNAME"))      # sample</t>
+  </si>
+  <si>
+    <t>main.py</t>
+  </si>
+  <si>
+    <t>load_dotenv()</t>
+  </si>
+  <si>
+    <t>The collections module in Python is one of the most important standard library modules. It provides specialized container datatypes that extend the functionality of Python’s built-in data structures like dict, list, set, and tuple.</t>
+  </si>
+  <si>
+    <t>collections</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>A dictionary subclass for counting hashable objects.</t>
+  </si>
+  <si>
+    <t>from collections import Counter
+data = ['a', 'b', 'a', 'c', 'b', 'a']
+counter = Counter(data)
+print(counter)        # Counter({'a': 3, 'b': 2, 'c': 1})
+print(counter.most_common(1))  # [('a', 3)]</t>
+  </si>
+  <si>
+    <t>Counter({'a': 3, 'b': 2, 'c': 1})
+[('a', 3)]</t>
+  </si>
+  <si>
+    <t>from collections import defaultdict
+dd = defaultdict(int)
+dd['apple'] += 1
+print(dd)  # defaultdict(&lt;class 'int'&gt;, {'apple': 1})</t>
+  </si>
+  <si>
+    <t>defaultdict</t>
+  </si>
+  <si>
+    <t>Like a normal dictionary, but provides a default value for missing keys.</t>
+  </si>
+  <si>
+    <t>defaultdict(&lt;class 'int'&gt;, {'apple': 1})</t>
+  </si>
+  <si>
+    <t>OrderedDict</t>
+  </si>
+  <si>
+    <t>Keeps track of the order keys were added.</t>
+  </si>
+  <si>
+    <t>from collections import OrderedDict
+od = OrderedDict()
+od['a'] = 1
+od['b'] = 2
+od['c'] = 3
+print(od)  # OrderedDict([('a', 1), ('b', 2), ('c', 3)])</t>
+  </si>
+  <si>
+    <t>OrderedDict([('a', 1), ('b', 2), ('c', 3)])</t>
+  </si>
+  <si>
+    <r>
+      <t>deque</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Double-Ended Queue)</t>
+    </r>
+  </si>
+  <si>
+    <t>A list-like container with fast appends and pops from both ends.</t>
+  </si>
+  <si>
+    <t>from collections import deque
+dq = deque([1, 2, 3])
+dq.append(4)
+dq.appendleft(0)
+print(dq)  # deque([0, 1, 2, 3, 4])
+dq.pop()
+dq.popleft()
+print(dq)  # deque([1, 2, 3])</t>
+  </si>
+  <si>
+    <t>deque([0, 1, 2, 3, 4])
+deque([1, 2, 3])</t>
+  </si>
+  <si>
+    <t>from collections import namedtuple
+Point = namedtuple('Point', 'x y')
+p = Point(10, 20)
+print(p.x, p.y)  # 10 20</t>
+  </si>
+  <si>
+    <t>10 20</t>
+  </si>
+  <si>
+    <t>Creates tuple subclasses with named fields (better readability than normal tuples).</t>
+  </si>
+  <si>
+    <t>namedtuple</t>
+  </si>
+  <si>
+    <t>from docx import *
+#python-docx
+def extract_text_from_word(file_path):
+    doc = Document(file_path)
+    full_text = []
+    for para in doc.paragraphs:
+        full_text.append(para.text)
+    return "\n".join(full_text)
+# Usage
+word_text = extract_text_from_word(r"C:\Harikrishnan\Document\Learning\Python\Resume Filtering System\Job Description\JD - Junior Python developer.docx")
+print(word_text)</t>
+  </si>
+  <si>
+    <t>Job Title: Junior Python Developer – AIS Vessel Tracking &amp; Seachart Digitization
+Experience: 1-2 Years
+Location: DEME Group, Chennai
+Employment Type: Full-timeJob Summary:
+We are looking for a passionate and detail-oriented Junior Python Developer with 2 years of professional experience to join our team. The ideal candidate will work on AIS vessel tracking and seachart digitization projects. The role requires strong Python skills, familiarity with SQL, and a good understanding of data handling and geospatial processing.
+Key Responsibilities:
+Develop and maintain Python scripts and tools for AIS (Automatic Identification System) vessel tracking data analysis.
+Digitize and convert marine seacharts into usable digital formats using geospatial libraries and tools.
+Write optimized SQL queries and manage spatial databases.
+Collaborate with cross-functional teams to understand requirements and deliver accurate digital outputs.
+Ensure data accuracy, integrity, and visualization quality in projects.
+Participate in code reviews, testing, and continuous improvement activities.
+Required Skills:
+Proficiency in Python (including libraries such as Pandas, Numpy, and optionally Geopandas, Shapely, etc.).
+Working knowledge of PGAdmin and SQL.
+Strong analytical and logical thinking skills.
+Understanding of AIS data, vessel movement patterns, and mapping concepts (preferred but not mandatory).
+Good understanding of data structures, file handling, and data transformation.
+Basic knowledge of GIS tools or libraries is an advantage.
+Strong communication skills and ability to work well in a collaborative team environment.</t>
+  </si>
+  <si>
+    <t>extract_text_from_word</t>
+  </si>
+  <si>
+    <t>os.path.splitext(filename)</t>
+  </si>
+  <si>
+    <t>os.path.splitext()</t>
+  </si>
+  <si>
+    <t>import os
+files = ['JD - Junior Python developer.docx']
+filename = files[0]   # take first element from list
+result = os.path.splitext(filename)
+for i in result:
+    print(i)</t>
+  </si>
+  <si>
+    <t>JD - Junior Python developer
+.docx</t>
+  </si>
+  <si>
+    <t>It is used to separate a file name and its extension. It returns a tuple: (root, ext), where root is the name without extension and ext is the extension with dot.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1140,16 +2491,30 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1175,10 +2540,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1202,14 +2568,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="47" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1223,6 +2604,165 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>182880</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>472440</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>2255520</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>1158240</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Object 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1541,6 +3081,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C38307A-8680-4791-BBD8-DB9BC6C483F1}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="93.6">
+      <c r="A4" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="78">
+      <c r="A5" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="109.2">
+      <c r="A6" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="140.4">
+      <c r="A7" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="78">
+      <c r="A8" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C934045-05FF-4210-8158-62207BC62C8B}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -1575,14 +3257,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="31.2">
       <c r="A3" s="4" t="s">
@@ -1605,7 +3287,7 @@
       <c r="B4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1622,7 +3304,7 @@
       <c r="B5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1639,30 +3321,30 @@
       <c r="B6" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>138</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="62.4">
       <c r="A7" s="4" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>143</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -1673,13 +3355,13 @@
       <c r="B8" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1690,13 +3372,13 @@
       <c r="B9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1707,7 +3389,7 @@
       <c r="B10" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1724,7 +3406,7 @@
       <c r="B11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1743,7 +3425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEC7921-BA36-4A45-8BC0-808C0D35D2A9}">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -1778,14 +3460,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="109.2">
       <c r="A3" s="4" t="s">
@@ -1894,14 +3576,14 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="37.200000000000003">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" ht="93.6">
       <c r="A11" s="4" t="s">
@@ -1981,14 +3663,14 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="37.200000000000003">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" ht="93.6">
       <c r="A17" s="4" t="s">
@@ -2120,14 +3802,14 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="37.200000000000003">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" ht="156">
       <c r="A27" s="4" t="s">
@@ -2206,14 +3888,14 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="37.200000000000003">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:5" ht="109.2">
       <c r="A33" s="4" t="s">
@@ -2242,9 +3924,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FFEDB6-E341-4091-95D4-D478ABE8D506}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2252,7 +3934,1467 @@
         <v>42</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{0F9E77A4-61D3-48E7-9251-D0798BD5E18A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C6E5AF-699F-402C-9589-CFFA4B9F86EA}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="109.2">
+      <c r="A4" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="2" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="409.6">
+      <c r="A5" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="409.6">
+      <c r="A6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1025" r:id="rId4">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>182880</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>472440</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>2255520</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1158240</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Document" dvAspect="DVASPECT_ICON" shapeId="1025" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B2D533-6BED-41FA-88F3-447029259AF0}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="78">
+      <c r="A4" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2">
+      <c r="A5" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="327.60000000000002">
+      <c r="A6" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.6">
+      <c r="A7" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BEB66B-D250-4C98-A088-DEE6EC94D3A0}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="93.6">
+      <c r="A4" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2">
+      <c r="A5" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="46.8">
+      <c r="A6" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="46.8">
+      <c r="A7" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9814D58D-ACB5-48D2-873F-6EC44E5F3AAE}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.69921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="140.4">
+      <c r="A5" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED627A0A-2B6B-4427-B011-84981C8D1648}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="202.8">
+      <c r="A4" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08AF8075-EF27-47EF-A398-AC95BFC575FB}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="21" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="62.4">
+      <c r="A4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="46.8">
+      <c r="A5" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="62.4">
+      <c r="A6" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="46.8">
+      <c r="A7" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="31.2">
+      <c r="A8" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="46.8">
+      <c r="A9" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="46.8">
+      <c r="A10" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="93.6">
+      <c r="A11" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="62.4">
+      <c r="A12" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="62.4">
+      <c r="A13" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4"/>
+      <c r="B15" s="3"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="3"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5CC089-3DDF-4BCF-BA57-9FC65676C7FD}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A3" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="31.2">
+      <c r="A4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2">
+      <c r="A5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" ht="46.8">
+      <c r="A6" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="124.8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="62.4">
+      <c r="A8" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="2" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="31.2">
+      <c r="A9" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E9" s="2" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="46.8">
+      <c r="A10" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10" s="2" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="46.8">
+      <c r="A11" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" s="2" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11" s="1" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="78">
+      <c r="A12" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="2" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F12" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="46.8">
+      <c r="A13" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="46.8">
+      <c r="A14" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="46.8">
+      <c r="A15" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="93.6">
+      <c r="A16" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="37.200000000000003">
+      <c r="A17" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" spans="1:6" ht="31.2">
+      <c r="A18" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="31.2">
+      <c r="A19" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="31.2">
+      <c r="A20" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="31.2">
+      <c r="A21" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="31.2">
+      <c r="A22" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="13">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3184C4F-4668-45A9-8A0B-A9BD2B38FA41}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="18.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.3984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="8" customFormat="1" ht="37.200000000000003">
+      <c r="A2" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="46.8">
+      <c r="A3" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="46.8">
+      <c r="A4" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="31.2">
+      <c r="A5" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="31.2">
+      <c r="A6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="62.4">
+      <c r="A7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="46.8">
+      <c r="A8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="62.4">
+      <c r="A9" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="62.4">
+      <c r="A10" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="62.4">
+      <c r="A11" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="78">
+      <c r="A12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>